--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\AndroidStudioProjects\qamid-diplom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DFA8398-3CB3-482F-941E-52D4DED374EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F1A217-6BB3-447B-8B2F-1CB27E0E0FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{99ED7372-FA73-4A7A-B326-16BEA7D4A0D6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{99ED7372-FA73-4A7A-B326-16BEA7D4A0D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="246">
   <si>
     <t>ID</t>
   </si>
@@ -833,6 +833,56 @@
 4. Поле заполняется
 5. Поле заполняется
 6. Открывается Панель управления со списком новостей, с обновленной записью, в которой дата создания соответствует текущей дате</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дефект!
+BUG-1
+</t>
+  </si>
+  <si>
+    <t>1. Открывается боковое меню с кнопками Main, News, About
+2. Открывается раздел News
+3. Открывается боковое меню с кнопками Main (кликабелен), News (кликабелен), About (некликабелен)</t>
+  </si>
+  <si>
+    <t>1. Открывается боковое меню с кнопками Main, News, About
+2. Кнопка About некликабельна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дефект!
+BUG-1 (дубликат)
+</t>
+  </si>
+  <si>
+    <t>1. Открывается раздел создания новости, где чекбокс Active некликабелен</t>
+  </si>
+  <si>
+    <t>Дефект!
+BUG-2</t>
+  </si>
+  <si>
+    <t>Дефект!
+BUG-3</t>
+  </si>
+  <si>
+    <t>1. Поле заполняется
+2. Поле заполняется
+3. Поле заполняется
+4. Поле заполняется
+5. Поле заполняется
+6. Открывается Панель управления со списком новостей, с обновленной записью, в которой дата создания равна 13.01.58025</t>
+  </si>
+  <si>
+    <t>1. Поле заполняется
+2. Поле заполняется
+3. Поле заполняется
+4. Поле заполняется
+5. Поле заполняется
+6. Открывается Панель управления со списком новостей, с новой записью, в которой дата создания равняется 14.01.58025</t>
+  </si>
+  <si>
+    <t>Дефект!
+BUG-3 (дубликат)</t>
   </si>
 </sst>
 </file>
@@ -1197,8 +1247,8 @@
     <col min="4" max="4" width="11.88671875" customWidth="1"/>
     <col min="5" max="5" width="30.109375" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.88671875" customWidth="1"/>
+    <col min="8" max="8" width="32.77734375" customWidth="1"/>
     <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1257,7 +1307,9 @@
       <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1285,7 +1337,9 @@
       <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1313,7 +1367,9 @@
       <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="I4" s="1" t="s">
         <v>17</v>
       </c>
@@ -1341,7 +1397,9 @@
       <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="I5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1369,7 +1427,9 @@
       <c r="G6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="I6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1397,7 +1457,9 @@
       <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="I7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1425,13 +1487,15 @@
       <c r="G8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="I8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -1453,13 +1517,15 @@
       <c r="G9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
@@ -1481,13 +1547,15 @@
       <c r="G10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="I10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
@@ -1509,13 +1577,17 @@
       <c r="G11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="I11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="J11" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1537,13 +1609,15 @@
       <c r="G12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="I12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
@@ -1565,7 +1639,9 @@
       <c r="G13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="I13" s="1" t="s">
         <v>17</v>
       </c>
@@ -1593,13 +1669,15 @@
       <c r="G14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>67</v>
       </c>
@@ -1621,13 +1699,15 @@
       <c r="G15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="I15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>71</v>
       </c>
@@ -1649,13 +1729,15 @@
       <c r="G16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="I16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>75</v>
       </c>
@@ -1677,11 +1759,15 @@
       <c r="G17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="1"/>
+      <c r="H17" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="I17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -1705,7 +1791,9 @@
       <c r="G18" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="1"/>
+      <c r="H18" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="I18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1733,13 +1821,15 @@
       <c r="G19" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="1"/>
+      <c r="H19" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="I19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>86</v>
       </c>
@@ -1761,13 +1851,15 @@
       <c r="G20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="1"/>
+      <c r="H20" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="I20" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="216" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>90</v>
       </c>
@@ -1789,13 +1881,15 @@
       <c r="G21" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="I21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>96</v>
       </c>
@@ -1817,7 +1911,9 @@
       <c r="G22" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="H22" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="I22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1845,7 +1941,9 @@
       <c r="G23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H23" s="1"/>
+      <c r="H23" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="I23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1873,7 +1971,9 @@
       <c r="G24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="1"/>
+      <c r="H24" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="I24" s="1" t="s">
         <v>109</v>
       </c>
@@ -1881,7 +1981,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>111</v>
       </c>
@@ -1903,7 +2003,9 @@
       <c r="G25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H25" s="1"/>
+      <c r="H25" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="I25" s="1" t="s">
         <v>109</v>
       </c>
@@ -1933,13 +2035,15 @@
       <c r="G26" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H26" s="1"/>
+      <c r="H26" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="I26" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>118</v>
       </c>
@@ -1961,13 +2065,17 @@
       <c r="G27" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H27" s="1"/>
+      <c r="H27" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="I27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="J27" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>121</v>
       </c>
@@ -1989,13 +2097,15 @@
       <c r="G28" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H28" s="1"/>
+      <c r="H28" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="I28" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>124</v>
       </c>
@@ -2017,13 +2127,15 @@
       <c r="G29" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H29" s="1"/>
+      <c r="H29" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="I29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>127</v>
       </c>
@@ -2045,13 +2157,15 @@
       <c r="G30" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H30" s="1"/>
+      <c r="H30" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="I30" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>131</v>
       </c>
@@ -2073,13 +2187,15 @@
       <c r="G31" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H31" s="1"/>
+      <c r="H31" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="I31" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>135</v>
       </c>
@@ -2101,7 +2217,9 @@
       <c r="G32" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H32" s="1"/>
+      <c r="H32" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="I32" s="1" t="s">
         <v>109</v>
       </c>
@@ -2109,7 +2227,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>138</v>
       </c>
@@ -2131,7 +2249,9 @@
       <c r="G33" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H33" s="1"/>
+      <c r="H33" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="I33" s="1" t="s">
         <v>109</v>
       </c>
@@ -2139,7 +2259,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>142</v>
       </c>
@@ -2161,13 +2281,15 @@
       <c r="G34" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H34" s="1"/>
+      <c r="H34" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="I34" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>146</v>
       </c>
@@ -2189,13 +2311,15 @@
       <c r="G35" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H35" s="1"/>
+      <c r="H35" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="I35" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>149</v>
       </c>
@@ -2217,13 +2341,15 @@
       <c r="G36" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H36" s="1"/>
+      <c r="H36" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="I36" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J36" s="1"/>
     </row>
-    <row r="37" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>152</v>
       </c>
@@ -2245,13 +2371,15 @@
       <c r="G37" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H37" s="1"/>
+      <c r="H37" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="I37" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J37" s="1"/>
     </row>
-    <row r="38" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>155</v>
       </c>
@@ -2273,7 +2401,9 @@
       <c r="G38" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H38" s="1"/>
+      <c r="H38" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="I38" s="1" t="s">
         <v>17</v>
       </c>
@@ -2339,7 +2469,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="288" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>166</v>
       </c>
@@ -2361,13 +2491,15 @@
       <c r="G41" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="H41" s="1"/>
+      <c r="H41" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="I41" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>170</v>
       </c>
@@ -2389,13 +2521,17 @@
       <c r="G42" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H42" s="1"/>
+      <c r="H42" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="I42" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="J42" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>173</v>
       </c>
@@ -2417,13 +2553,15 @@
       <c r="G43" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H43" s="1"/>
+      <c r="H43" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="I43" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>178</v>
       </c>
@@ -2445,13 +2583,15 @@
       <c r="G44" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="H44" s="1"/>
+      <c r="H44" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="I44" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="1:10" ht="216" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>182</v>
       </c>
@@ -2473,13 +2613,15 @@
       <c r="G45" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H45" s="1"/>
+      <c r="H45" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="I45" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>187</v>
       </c>
@@ -2501,13 +2643,15 @@
       <c r="G46" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="H46" s="1"/>
+      <c r="H46" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="I46" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>190</v>
       </c>
@@ -2529,7 +2673,9 @@
       <c r="G47" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H47" s="1"/>
+      <c r="H47" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="I47" s="1" t="s">
         <v>17</v>
       </c>
@@ -2557,7 +2703,9 @@
       <c r="G48" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H48" s="1"/>
+      <c r="H48" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="I48" s="1" t="s">
         <v>17</v>
       </c>
@@ -2585,7 +2733,9 @@
       <c r="G49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H49" s="1"/>
+      <c r="H49" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="I49" s="1" t="s">
         <v>109</v>
       </c>
@@ -2593,7 +2743,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>197</v>
       </c>
@@ -2615,7 +2765,9 @@
       <c r="G50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H50" s="1"/>
+      <c r="H50" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="I50" s="1" t="s">
         <v>109</v>
       </c>
@@ -2645,13 +2797,15 @@
       <c r="G51" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H51" s="1"/>
+      <c r="H51" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="I51" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>201</v>
       </c>
@@ -2673,13 +2827,15 @@
       <c r="G52" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H52" s="1"/>
+      <c r="H52" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="I52" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>204</v>
       </c>
@@ -2701,13 +2857,15 @@
       <c r="G53" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H53" s="1"/>
+      <c r="H53" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="I53" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>207</v>
       </c>
@@ -2729,13 +2887,15 @@
       <c r="G54" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="H54" s="1"/>
+      <c r="H54" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="I54" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>210</v>
       </c>
@@ -2757,13 +2917,15 @@
       <c r="G55" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H55" s="1"/>
+      <c r="H55" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="I55" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>213</v>
       </c>
@@ -2785,13 +2947,15 @@
       <c r="G56" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H56" s="1"/>
+      <c r="H56" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="I56" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>217</v>
       </c>
@@ -2813,7 +2977,9 @@
       <c r="G57" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H57" s="1"/>
+      <c r="H57" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="I57" s="1" t="s">
         <v>109</v>
       </c>
@@ -2821,7 +2987,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>219</v>
       </c>
@@ -2843,7 +3009,9 @@
       <c r="G58" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H58" s="1"/>
+      <c r="H58" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="I58" s="1" t="s">
         <v>109</v>
       </c>
@@ -2851,7 +3019,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>221</v>
       </c>
@@ -2873,13 +3041,15 @@
       <c r="G59" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H59" s="1"/>
+      <c r="H59" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="I59" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>225</v>
       </c>
@@ -2901,13 +3071,15 @@
       <c r="G60" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H60" s="1"/>
+      <c r="H60" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="I60" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>228</v>
       </c>
@@ -2929,13 +3101,15 @@
       <c r="G61" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H61" s="1"/>
+      <c r="H61" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="I61" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="1:10" ht="288" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>230</v>
       </c>
@@ -2957,13 +3131,15 @@
       <c r="G62" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="H62" s="1"/>
+      <c r="H62" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="I62" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>233</v>
       </c>
@@ -2985,11 +3161,15 @@
       <c r="G63" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="H63" s="1"/>
+      <c r="H63" s="1" t="s">
+        <v>243</v>
+      </c>
       <c r="I63" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J63" s="1"/>
+      <c r="J63" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
